--- a/artfynd/A 60246-2021 artfynd.xlsx
+++ b/artfynd/A 60246-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60246-2021 artfynd.xlsx
+++ b/artfynd/A 60246-2021 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96785963</v>
+        <v>96785964</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>417092.6538888349</v>
+        <v>417092</v>
       </c>
       <c r="R2" t="n">
-        <v>7039327.882746263</v>
+        <v>7039328</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2016-10-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-10-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>på granlåga (25 cm i diameter,  120 år )</t>
+          <t>på gammal granlåga (25 cm i diameter,  120 år )</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -802,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96785964</v>
+        <v>104665855</v>
       </c>
       <c r="B3" t="n">
-        <v>89577</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordväst om Krok, 5-7 km öster om Kalls kyrka, Jmt</t>
+          <t>Svarttjärn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>417092.6538888349</v>
+        <v>417294</v>
       </c>
       <c r="R3" t="n">
-        <v>7039327.882746263</v>
+        <v>7039512</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-10-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-10-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,31 +868,16 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>i gammal granskog (ca 120-150 år) på friskfuktig mark</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>på gammal granlåga (25 cm i diameter,  120 år )</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Christina Nysten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -932,12 +887,7 @@
         <v>104665809</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416895.6152806152</v>
+        <v>416896</v>
       </c>
       <c r="R4" t="n">
-        <v>7039156.346759312</v>
+        <v>7039157</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,19 +952,9 @@
           <t>2022-11-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104665845</v>
+        <v>107240216</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,45 +992,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarttjärn, Jmt</t>
+          <t>Krok, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418199.0923969702</v>
+        <v>417419</v>
       </c>
       <c r="R5" t="n">
-        <v>7040439.105304372</v>
+        <v>7039641</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,27 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2023-03-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,27 +1066,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein, Magnus Wadstein, Ebba Wadstein</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107240215</v>
+        <v>104665845</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,37 +1089,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Krok, Jmt</t>
+          <t>Svarttjärn, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>417305.6672054169</v>
+        <v>418199</v>
       </c>
       <c r="R6" t="n">
-        <v>7039546.410145209</v>
+        <v>7040439</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,22 +1151,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,65 +1176,68 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Magnus Wadstein, Ebba Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107240216</v>
+        <v>104665846</v>
       </c>
       <c r="B7" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>102125</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Krok, Jmt</t>
+          <t>Svarttjärn, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>417419.1704497467</v>
+        <v>417286</v>
       </c>
       <c r="R7" t="n">
-        <v>7039640.958180222</v>
+        <v>7039508</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1348,22 +1261,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,12 +1281,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Magnus Wadstein, Ebba Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 60246-2021 artfynd.xlsx
+++ b/artfynd/A 60246-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785964</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104665809</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104665855</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240216</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104665845</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,8 +1320,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104665846</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>